--- a/artfynd/A 34283-2024 artfynd.xlsx
+++ b/artfynd/A 34283-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127317426</v>
       </c>
       <c r="B2" t="n">
-        <v>58334</v>
+        <v>58338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127317382</v>
       </c>
       <c r="B3" t="n">
-        <v>58195</v>
+        <v>58199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127317347</v>
       </c>
       <c r="B4" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127317430</v>
       </c>
       <c r="B5" t="n">
-        <v>58334</v>
+        <v>58338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>127317337</v>
       </c>
       <c r="B6" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127317336</v>
       </c>
       <c r="B7" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34283-2024 artfynd.xlsx
+++ b/artfynd/A 34283-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127317426</v>
       </c>
       <c r="B2" t="n">
-        <v>58338</v>
+        <v>58340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127317382</v>
       </c>
       <c r="B3" t="n">
-        <v>58199</v>
+        <v>58201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127317347</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127317430</v>
       </c>
       <c r="B5" t="n">
-        <v>58338</v>
+        <v>58340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127317337</v>
+        <v>127317336</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483566</v>
+        <v>483472</v>
       </c>
       <c r="R6" t="n">
-        <v>6539718</v>
+        <v>6539711</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127317336</v>
+        <v>127317337</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483472</v>
+        <v>483566</v>
       </c>
       <c r="R7" t="n">
-        <v>6539711</v>
+        <v>6539718</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 34283-2024 artfynd.xlsx
+++ b/artfynd/A 34283-2024 artfynd.xlsx
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127317336</v>
+        <v>127317337</v>
       </c>
       <c r="B6" t="n">
         <v>58033</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483472</v>
+        <v>483566</v>
       </c>
       <c r="R6" t="n">
-        <v>6539711</v>
+        <v>6539718</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127317337</v>
+        <v>127317336</v>
       </c>
       <c r="B7" t="n">
         <v>58033</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483566</v>
+        <v>483472</v>
       </c>
       <c r="R7" t="n">
-        <v>6539718</v>
+        <v>6539711</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 34283-2024 artfynd.xlsx
+++ b/artfynd/A 34283-2024 artfynd.xlsx
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127317337</v>
+        <v>127317336</v>
       </c>
       <c r="B6" t="n">
         <v>58033</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483566</v>
+        <v>483472</v>
       </c>
       <c r="R6" t="n">
-        <v>6539718</v>
+        <v>6539711</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127317336</v>
+        <v>127317337</v>
       </c>
       <c r="B7" t="n">
         <v>58033</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483472</v>
+        <v>483566</v>
       </c>
       <c r="R7" t="n">
-        <v>6539711</v>
+        <v>6539718</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 34283-2024 artfynd.xlsx
+++ b/artfynd/A 34283-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127317426</v>
       </c>
       <c r="B2" t="n">
-        <v>58340</v>
+        <v>58343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127317382</v>
       </c>
       <c r="B3" t="n">
-        <v>58201</v>
+        <v>58204</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127317347</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127317430</v>
       </c>
       <c r="B5" t="n">
-        <v>58340</v>
+        <v>58343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127317336</v>
+        <v>127317337</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483472</v>
+        <v>483566</v>
       </c>
       <c r="R6" t="n">
-        <v>6539711</v>
+        <v>6539718</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127317337</v>
+        <v>127317336</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483566</v>
+        <v>483472</v>
       </c>
       <c r="R7" t="n">
-        <v>6539718</v>
+        <v>6539711</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 34283-2024 artfynd.xlsx
+++ b/artfynd/A 34283-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127317426</v>
       </c>
       <c r="B2" t="n">
-        <v>58343</v>
+        <v>58349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127317382</v>
       </c>
       <c r="B3" t="n">
-        <v>58204</v>
+        <v>58210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127317347</v>
       </c>
       <c r="B4" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127317430</v>
       </c>
       <c r="B5" t="n">
-        <v>58343</v>
+        <v>58349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>127317337</v>
       </c>
       <c r="B6" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127317336</v>
       </c>
       <c r="B7" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34283-2024 artfynd.xlsx
+++ b/artfynd/A 34283-2024 artfynd.xlsx
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127317337</v>
+        <v>127317336</v>
       </c>
       <c r="B6" t="n">
         <v>58042</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483566</v>
+        <v>483472</v>
       </c>
       <c r="R6" t="n">
-        <v>6539718</v>
+        <v>6539711</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127317336</v>
+        <v>127317337</v>
       </c>
       <c r="B7" t="n">
         <v>58042</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483472</v>
+        <v>483566</v>
       </c>
       <c r="R7" t="n">
-        <v>6539711</v>
+        <v>6539718</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 34283-2024 artfynd.xlsx
+++ b/artfynd/A 34283-2024 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127317426</v>
+        <v>127317382</v>
       </c>
       <c r="B2" t="n">
-        <v>58349</v>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483645</v>
+        <v>483609</v>
       </c>
       <c r="R2" t="n">
-        <v>6539741</v>
+        <v>6539729</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127317382</v>
+        <v>127317336</v>
       </c>
       <c r="B3" t="n">
-        <v>58210</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483609</v>
+        <v>483472</v>
       </c>
       <c r="R3" t="n">
-        <v>6539729</v>
+        <v>6539711</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127317347</v>
+        <v>127317337</v>
       </c>
       <c r="B4" t="n">
-        <v>58042</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483531</v>
+        <v>483566</v>
       </c>
       <c r="R4" t="n">
-        <v>6539694</v>
+        <v>6539718</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127317430</v>
+        <v>127317347</v>
       </c>
       <c r="B5" t="n">
-        <v>58349</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,16 +1004,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483556</v>
+        <v>483531</v>
       </c>
       <c r="R5" t="n">
-        <v>6539718</v>
+        <v>6539694</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127317336</v>
+        <v>127317426</v>
       </c>
       <c r="B6" t="n">
-        <v>58042</v>
+        <v>58636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,16 +1110,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483472</v>
+        <v>483645</v>
       </c>
       <c r="R6" t="n">
-        <v>6539711</v>
+        <v>6539741</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127317337</v>
+        <v>127317430</v>
       </c>
       <c r="B7" t="n">
-        <v>58042</v>
+        <v>58636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483566</v>
+        <v>483556</v>
       </c>
       <c r="R7" t="n">
         <v>6539718</v>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 34283-2024 artfynd.xlsx
+++ b/artfynd/A 34283-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317382</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317336</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317337</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317347</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317426</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127317430</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>